--- a/data/trans_orig/P16A_n_R3-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P16A_n_R3-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido cinco o más medicamentos en las dos últimas semanas en 2007</t>
+          <t>Población que ha consumido cinco o más medicamentos en las dos últimas semanas en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22617</t>
+          <t>22619</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>44269</t>
+          <t>45430</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>50019</t>
+          <t>49150</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>81355</t>
+          <t>80503</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>80057</t>
+          <t>78184</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>116795</t>
+          <t>114873</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,89%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>987454</t>
+          <t>986293</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1009106</t>
+          <t>1009104</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1233758</t>
+          <t>1234610</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1265094</t>
+          <t>1265963</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2230040</t>
+          <t>2231962</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2266778</t>
+          <t>2268651</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,67%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>6237</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21531</t>
+          <t>20301</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13021</t>
+          <t>14121</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31708</t>
+          <t>33658</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>23262</t>
+          <t>23580</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>47075</t>
+          <t>46491</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1671882</t>
+          <t>1673112</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1687190</t>
+          <t>1687176</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1555965</t>
+          <t>1554015</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1574652</t>
+          <t>1573552</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3234011</t>
+          <t>3234595</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3257824</t>
+          <t>3257506</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,28%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1779</t>
+          <t>1760</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11440</t>
+          <t>10135</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5677</t>
+          <t>5616</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1983</t>
+          <t>2092</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12137</t>
+          <t>12350</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,2%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>539968</t>
+          <t>541273</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>549629</t>
+          <t>549648</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>470735</t>
+          <t>470796</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1015683</t>
+          <t>1015470</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1025837</t>
+          <t>1025728</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>99,8%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>36592</t>
+          <t>36732</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>64528</t>
+          <t>62924</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>69379</t>
+          <t>71158</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>108246</t>
+          <t>107516</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>113981</t>
+          <t>113739</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>161115</t>
+          <t>160060</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3212015</t>
+          <t>3213619</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3239951</t>
+          <t>3239811</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3270951</t>
+          <t>3271681</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3309818</t>
+          <t>3308039</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6494626</t>
+          <t>6495681</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6541760</t>
+          <t>6542002</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido cinco o más medicamentos en las dos últimas semanas en 2012</t>
+          <t>Población que ha consumido cinco o más medicamentos en las dos últimas semanas en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>31317</t>
+          <t>30725</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>60518</t>
+          <t>59917</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>121638</t>
+          <t>119668</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>168297</t>
+          <t>169415</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>158602</t>
+          <t>159087</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>212328</t>
+          <t>212951</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,21%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>914125</t>
+          <t>914726</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>943326</t>
+          <t>943918</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1169500</t>
+          <t>1168382</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1216159</t>
+          <t>1218129</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,42%</t>
+          <t>87,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>91,05%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2100112</t>
+          <t>2099489</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2153838</t>
+          <t>2153353</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>90,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>93,12%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6837</t>
+          <t>6295</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22272</t>
+          <t>21954</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16197</t>
+          <t>16144</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>34880</t>
+          <t>36346</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>26900</t>
+          <t>26744</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>53112</t>
+          <t>52056</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,4%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1941685</t>
+          <t>1942003</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1957120</t>
+          <t>1957662</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1722923</t>
+          <t>1721457</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1741606</t>
+          <t>1741659</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3668648</t>
+          <t>3669704</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3694860</t>
+          <t>3695016</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1852</t>
+          <t>1846</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15425</t>
+          <t>16309</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4170</t>
+          <t>4121</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17411</t>
+          <t>16535</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7482</t>
+          <t>7619</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28682</t>
+          <t>26765</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>465756</t>
+          <t>464872</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>479329</t>
+          <t>479335</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>441220</t>
+          <t>442096</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>454461</t>
+          <t>454510</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>911131</t>
+          <t>913048</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>932331</t>
+          <t>932194</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,19%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>47229</t>
+          <t>47429</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>84021</t>
+          <t>81442</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>151835</t>
+          <t>153399</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>203366</t>
+          <t>204901</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>207937</t>
+          <t>209936</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>273502</t>
+          <t>271588</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,89%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3335761</t>
+          <t>3338340</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3372553</t>
+          <t>3372353</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3350864</t>
+          <t>3349329</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3402395</t>
+          <t>3400831</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6700510</t>
+          <t>6702424</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6766075</t>
+          <t>6764076</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>96,99%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido cinco o más medicamentos en las dos últimas semanas en 2016</t>
+          <t>Población que ha consumido cinco o más medicamentos en las dos últimas semanas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>28066</t>
+          <t>27166</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>50815</t>
+          <t>50778</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>79353</t>
+          <t>80924</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>119309</t>
+          <t>121326</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>112950</t>
+          <t>114539</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>159425</t>
+          <t>159163</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,1%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>703532</t>
+          <t>703569</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>726281</t>
+          <t>727181</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>875351</t>
+          <t>873334</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>915307</t>
+          <t>913736</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,02%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1589582</t>
+          <t>1589844</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1636057</t>
+          <t>1634468</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,88%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,45%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8665</t>
+          <t>8578</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24281</t>
+          <t>26022</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>33367</t>
+          <t>32750</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>60626</t>
+          <t>62073</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>45476</t>
+          <t>45834</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>78612</t>
+          <t>79784</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2052104</t>
+          <t>2050363</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2067720</t>
+          <t>2067807</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1927674</t>
+          <t>1926227</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1954933</t>
+          <t>1955550</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3986073</t>
+          <t>3984901</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4019209</t>
+          <t>4018851</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,87%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>927</t>
+          <t>941</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10017</t>
+          <t>10697</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3221</t>
+          <t>3769</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16042</t>
+          <t>16872</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5392</t>
+          <t>5307</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21571</t>
+          <t>21138</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>536869</t>
+          <t>536189</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>545959</t>
+          <t>545945</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>533098</t>
+          <t>532268</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>545919</t>
+          <t>545371</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1074456</t>
+          <t>1074889</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1090635</t>
+          <t>1090720</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,52%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>41885</t>
+          <t>42226</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>71831</t>
+          <t>71578</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>127532</t>
+          <t>127366</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>176603</t>
+          <t>178612</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5023,7 +5023,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>178032</t>
+          <t>179757</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>236488</t>
+          <t>236530</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,7 +5053,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3305787</t>
+          <t>3306040</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3335733</t>
+          <t>3335392</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3355497</t>
+          <t>3353488</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3404568</t>
+          <t>3404734</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6673230</t>
+          <t>6673188</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6731686</t>
+          <t>6729961</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,4%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido cinco o más medicamentos en las dos últimas semanas en 2023</t>
+          <t>Población que ha consumido cinco o más medicamentos en las dos últimas semanas en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>53087</t>
+          <t>52336</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>78662</t>
+          <t>78838</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>172020</t>
+          <t>170060</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>210101</t>
+          <t>210100</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>231787</t>
+          <t>232827</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>277995</t>
+          <t>278127</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>21,89%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>436276</t>
+          <t>436100</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>461851</t>
+          <t>462602</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,72%</t>
+          <t>84,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>89,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>545407</t>
+          <t>545408</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>583488</t>
+          <t>585448</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5710,7 +5710,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,23%</t>
+          <t>77,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>992451</t>
+          <t>992319</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1038659</t>
+          <t>1037619</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>78,12%</t>
+          <t>78,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,76%</t>
+          <t>81,67%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>51872</t>
+          <t>53118</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>95865</t>
+          <t>95933</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,7 +5900,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>85149</t>
+          <t>82957</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>137242</t>
+          <t>136273</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>152748</t>
+          <t>153953</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>222242</t>
+          <t>221302</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,89%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2194462</t>
+          <t>2194394</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2238455</t>
+          <t>2237209</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6018,7 +6018,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2100581</t>
+          <t>2101550</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2152674</t>
+          <t>2154866</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4305908</t>
+          <t>4306848</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4375402</t>
+          <t>4374197</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,6%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9021</t>
+          <t>9601</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22908</t>
+          <t>23401</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18052</t>
+          <t>17929</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>33745</t>
+          <t>33301</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>29763</t>
+          <t>29547</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>50264</t>
+          <t>50280</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,7 +6313,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>623715</t>
+          <t>623222</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>637602</t>
+          <t>637022</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>626718</t>
+          <t>627162</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>642411</t>
+          <t>642534</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1256822</t>
+          <t>1256806</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1277323</t>
+          <t>1277539</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6431,7 +6431,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,74%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>120105</t>
+          <t>121338</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>181987</t>
+          <t>181016</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>269676</t>
+          <t>267218</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>365618</t>
+          <t>361935</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>421596</t>
+          <t>418555</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>533233</t>
+          <t>535229</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,53%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3269902</t>
+          <t>3270873</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3331784</t>
+          <t>3330551</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3288176</t>
+          <t>3291859</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3384118</t>
+          <t>3386576</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>90,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6572450</t>
+          <t>6570454</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6684087</t>
+          <t>6687128</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>94,11%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A_n_R3-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P16A_n_R3-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22619</t>
+          <t>22362</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>45430</t>
+          <t>45530</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>49150</t>
+          <t>50282</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>80503</t>
+          <t>81602</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>78184</t>
+          <t>78225</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>114873</t>
+          <t>117015</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,99%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>986293</t>
+          <t>986193</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1009104</t>
+          <t>1009361</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1234610</t>
+          <t>1233511</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1265963</t>
+          <t>1264831</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2231962</t>
+          <t>2229820</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2268651</t>
+          <t>2268610</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6237</t>
+          <t>6135</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20301</t>
+          <t>19973</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14121</t>
+          <t>13458</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>33658</t>
+          <t>32022</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>23580</t>
+          <t>23009</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>46491</t>
+          <t>45539</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,39%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1673112</t>
+          <t>1673440</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1687176</t>
+          <t>1687278</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1554015</t>
+          <t>1555651</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1573552</t>
+          <t>1574215</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3234595</t>
+          <t>3235547</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3257506</t>
+          <t>3258077</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,3%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1760</t>
+          <t>1890</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10135</t>
+          <t>10555</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5616</t>
+          <t>5601</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2092</t>
+          <t>2127</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12350</t>
+          <t>11979</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>541273</t>
+          <t>540853</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>549648</t>
+          <t>549518</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>470796</t>
+          <t>470811</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1015470</t>
+          <t>1015841</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1025728</t>
+          <t>1025693</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,79%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>36732</t>
+          <t>36699</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>62924</t>
+          <t>66042</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>71158</t>
+          <t>71073</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>107516</t>
+          <t>109134</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>113739</t>
+          <t>114323</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>160060</t>
+          <t>159065</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3213619</t>
+          <t>3210501</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3239811</t>
+          <t>3239844</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3271681</t>
+          <t>3270063</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3308039</t>
+          <t>3308124</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6495681</t>
+          <t>6496676</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6542002</t>
+          <t>6541418</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,28%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>30725</t>
+          <t>31150</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>59917</t>
+          <t>59704</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>119668</t>
+          <t>121342</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>169415</t>
+          <t>168597</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>159087</t>
+          <t>160796</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>212951</t>
+          <t>217350</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,4%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>914726</t>
+          <t>914939</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>943918</t>
+          <t>943493</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1168382</t>
+          <t>1169200</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1218129</t>
+          <t>1216455</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>87,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>90,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2099489</t>
+          <t>2095090</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2153353</t>
+          <t>2151644</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>90,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>93,05%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6295</t>
+          <t>6519</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21954</t>
+          <t>23519</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16144</t>
+          <t>16257</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36346</t>
+          <t>37571</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>26744</t>
+          <t>26136</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>52056</t>
+          <t>49813</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1942003</t>
+          <t>1940438</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1957662</t>
+          <t>1957438</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,67%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1721457</t>
+          <t>1720232</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1741659</t>
+          <t>1741546</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3669704</t>
+          <t>3671947</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3695016</t>
+          <t>3695624</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,3%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1846</t>
+          <t>1855</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16309</t>
+          <t>16721</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4121</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16535</t>
+          <t>17146</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7619</t>
+          <t>7763</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26765</t>
+          <t>27136</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,89%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>464872</t>
+          <t>464460</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>479335</t>
+          <t>479326</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>442096</t>
+          <t>441485</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>454510</t>
+          <t>454631</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>913048</t>
+          <t>912677</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>932194</t>
+          <t>932050</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,17%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>47429</t>
+          <t>46683</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>81442</t>
+          <t>81837</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>153399</t>
+          <t>152226</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>204901</t>
+          <t>204426</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>209936</t>
+          <t>206524</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>271588</t>
+          <t>270897</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,88%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3338340</t>
+          <t>3337945</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3372353</t>
+          <t>3373099</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3349329</t>
+          <t>3349804</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3400831</t>
+          <t>3402004</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6702424</t>
+          <t>6703115</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6764076</t>
+          <t>6767488</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>97,04%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>27166</t>
+          <t>28380</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>50778</t>
+          <t>49996</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>80924</t>
+          <t>78331</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>121326</t>
+          <t>120476</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>114539</t>
+          <t>115839</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>159163</t>
+          <t>161572</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,24%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>703569</t>
+          <t>704351</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>727181</t>
+          <t>725967</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>873334</t>
+          <t>874184</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>913736</t>
+          <t>916329</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,8%</t>
+          <t>87,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1589844</t>
+          <t>1587435</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1634468</t>
+          <t>1633168</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,9%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,38%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8578</t>
+          <t>7653</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26022</t>
+          <t>25179</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>32750</t>
+          <t>33137</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>62073</t>
+          <t>60378</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>45834</t>
+          <t>45501</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>79784</t>
+          <t>77364</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,9%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2050363</t>
+          <t>2051206</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2067807</t>
+          <t>2068732</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1926227</t>
+          <t>1927922</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1955550</t>
+          <t>1955163</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3984901</t>
+          <t>3987321</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4018851</t>
+          <t>4019184</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,88%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>924</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10697</t>
+          <t>9256</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3769</t>
+          <t>3118</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16872</t>
+          <t>15779</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5307</t>
+          <t>5717</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21138</t>
+          <t>21221</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,94%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>536189</t>
+          <t>537630</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>545945</t>
+          <t>545962</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>532268</t>
+          <t>533361</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>545371</t>
+          <t>546022</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1074889</t>
+          <t>1074806</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1090720</t>
+          <t>1090310</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,48%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>42226</t>
+          <t>43022</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>71578</t>
+          <t>72037</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>127366</t>
+          <t>128988</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>178612</t>
+          <t>181362</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>179757</t>
+          <t>182396</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>236530</t>
+          <t>239961</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,47%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3306040</t>
+          <t>3305581</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3335392</t>
+          <t>3334596</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3353488</t>
+          <t>3350738</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3404734</t>
+          <t>3403112</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6673188</t>
+          <t>6669757</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6729961</t>
+          <t>6727322</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,36%</t>
         </is>
       </c>
     </row>
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>65188</t>
+          <t>69774</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>52336</t>
+          <t>58131</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>78838</t>
+          <t>84058</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>189408</t>
+          <t>201429</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>170060</t>
+          <t>184376</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>210100</t>
+          <t>220153</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>254596</t>
+          <t>271203</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>232827</t>
+          <t>245550</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>278127</t>
+          <t>295610</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>21,11%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>449750</t>
+          <t>508755</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>436100</t>
+          <t>494471</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>462602</t>
+          <t>520398</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>87,94%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,69%</t>
+          <t>85,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,84%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>566100</t>
+          <t>620609</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>545408</t>
+          <t>601885</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>585448</t>
+          <t>637662</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>74,93%</t>
+          <t>75,5%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>72,19%</t>
+          <t>73,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,49%</t>
+          <t>77,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1015850</t>
+          <t>1129364</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>992319</t>
+          <t>1104957</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1037619</t>
+          <t>1155017</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>79,96%</t>
+          <t>80,64%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>78,11%</t>
+          <t>78,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,67%</t>
+          <t>82,47%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>76488</t>
+          <t>80215</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>53118</t>
+          <t>66452</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>95933</t>
+          <t>97719</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>115277</t>
+          <t>126351</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>82957</t>
+          <t>111162</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>136273</t>
+          <t>144415</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>191765</t>
+          <t>206566</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>153953</t>
+          <t>185737</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>221302</t>
+          <t>229987</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,22%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2213839</t>
+          <t>2150351</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2194394</t>
+          <t>2132847</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2237209</t>
+          <t>2164114</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2122546</t>
+          <t>2045041</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2101550</t>
+          <t>2026977</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2154866</t>
+          <t>2060230</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>4336385</t>
+          <t>4195393</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4306848</t>
+          <t>4171972</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4374197</t>
+          <t>4216222</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>95,78%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>14861</t>
+          <t>17426</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9601</t>
+          <t>10943</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23401</t>
+          <t>25686</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>24530</t>
+          <t>28164</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17929</t>
+          <t>20664</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>33301</t>
+          <t>37958</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>39391</t>
+          <t>45590</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>29547</t>
+          <t>35169</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>50280</t>
+          <t>57737</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,99%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>631762</t>
+          <t>694161</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>623222</t>
+          <t>685901</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>637022</t>
+          <t>700644</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>635933</t>
+          <t>706713</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>627162</t>
+          <t>696919</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>642534</t>
+          <t>714213</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1267695</t>
+          <t>1400874</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1256806</t>
+          <t>1388727</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1277539</t>
+          <t>1411295</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,57%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>156537</t>
+          <t>167415</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>121338</t>
+          <t>146058</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>181016</t>
+          <t>192536</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>329215</t>
+          <t>355945</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>267218</t>
+          <t>328317</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>361935</t>
+          <t>382762</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>485752</t>
+          <t>523360</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>418555</t>
+          <t>486456</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>535229</t>
+          <t>561393</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,74%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3295352</t>
+          <t>3353268</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3270873</t>
+          <t>3328147</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3330551</t>
+          <t>3374625</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3324579</t>
+          <t>3372362</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3291859</t>
+          <t>3345545</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3386576</t>
+          <t>3399990</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>90,45%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>89,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>91,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>6619931</t>
+          <t>6725630</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6570454</t>
+          <t>6687597</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6687128</t>
+          <t>6762534</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>92,78%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>93,29%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
